--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2170,6 +2170,4375 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127669079</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>461787</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7041311</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127669095</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>462005</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7041127</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127669091</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>462074</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7041005</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127669088</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>461891</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7041546</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127669062</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>462111</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7041002</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127669077</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>461872</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7041556</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127669056</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>461996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7041113</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127669073</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>461824</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7041252</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127669060</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>462105</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7040991</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127669084</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>461929</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7041760</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127669076</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>461956</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7041566</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127669065</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>462058</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7041020</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127669080</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>461710</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7041300</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127669081</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>461655</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7041293</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127669078</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>461868</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7041553</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127669086</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>461915</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7041539</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127669090</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>461887</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7041257</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127669082</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>461773</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7041572</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127669072</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>461817</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7041252</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127669083</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>461785</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7041591</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127669070</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>461616</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7041389</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127669089</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>461855</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7041550</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127669097</v>
+      </c>
+      <c r="B37" t="n">
+        <v>88733</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>510</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>461933</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7041131</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127669096</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>462095</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7041036</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127669074</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91737</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>461699</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7041298</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127669053</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>461654</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7041431</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127669059</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>462135</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7040976</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127669094</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>461551</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7041522</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127669085</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>462009</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7041536</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127669064</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>462063</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7041008</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127669066</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>461928</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7041135</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127669055</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>461992</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7041200</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127669058</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>462135</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7040973</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127669093</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>461799</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7041221</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127669087</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>461899</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7041535</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127669068</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>461816</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7041233</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127669067</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>461932</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7041126</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127669069</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>461820</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7041262</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127669057</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>462115</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7041025</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127669063</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>462099</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7041019</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127669054</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>461774</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7041329</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127669075</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>461962</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7041573</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127669071</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>461583</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7041458</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127669046</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bredbyn S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>462042</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7041614</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2371,7 +2371,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669091</v>
+        <v>127669088</v>
       </c>
       <c r="B17" t="n">
         <v>91348</v>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462074</v>
+        <v>461891</v>
       </c>
       <c r="R17" t="n">
-        <v>7041005</v>
+        <v>7041546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669088</v>
+        <v>127669091</v>
       </c>
       <c r="B18" t="n">
         <v>91348</v>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461891</v>
+        <v>462074</v>
       </c>
       <c r="R18" t="n">
-        <v>7041546</v>
+        <v>7041005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R19" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,11 +2636,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,21 +2673,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2697,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R20" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,6 +2733,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,7 +2764,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669056</v>
+        <v>127669060</v>
       </c>
       <c r="B21" t="n">
         <v>57661</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461996</v>
+        <v>462105</v>
       </c>
       <c r="R21" t="n">
-        <v>7041113</v>
+        <v>7040991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,21 +2877,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R22" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,6 +2937,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669084</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461929</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3039,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B24" t="n">
-        <v>91348</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R24" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669065</v>
+        <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462058</v>
+        <v>461710</v>
       </c>
       <c r="R26" t="n">
-        <v>7041020</v>
+        <v>7041300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,7 +3356,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669080</v>
+        <v>127669081</v>
       </c>
       <c r="B27" t="n">
         <v>91326</v>
@@ -3396,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461710</v>
+        <v>461655</v>
       </c>
       <c r="R27" t="n">
-        <v>7041300</v>
+        <v>7041293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669081</v>
+        <v>127669065</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,21 +3464,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461655</v>
+        <v>462058</v>
       </c>
       <c r="R28" t="n">
-        <v>7041293</v>
+        <v>7041020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,6 +3524,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,7 +3749,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669090</v>
+        <v>127669082</v>
       </c>
       <c r="B31" t="n">
         <v>91348</v>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461887</v>
+        <v>461773</v>
       </c>
       <c r="R31" t="n">
-        <v>7041257</v>
+        <v>7041572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127669082</v>
+        <v>127669090</v>
       </c>
       <c r="B32" t="n">
         <v>91348</v>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461773</v>
+        <v>461887</v>
       </c>
       <c r="R32" t="n">
-        <v>7041572</v>
+        <v>7041257</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669053</v>
+        <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461654</v>
+        <v>461551</v>
       </c>
       <c r="R40" t="n">
-        <v>7041431</v>
+        <v>7041522</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,11 +4704,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4837,10 +4832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669094</v>
+        <v>127669053</v>
       </c>
       <c r="B42" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,21 +4843,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4872,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461551</v>
+        <v>461654</v>
       </c>
       <c r="R42" t="n">
-        <v>7041522</v>
+        <v>7041431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,6 +4903,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669085</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462009</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041536</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,6 +5005,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,7 +5036,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
         <v>57661</v>
@@ -5066,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669055</v>
+        <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461992</v>
+        <v>462009</v>
       </c>
       <c r="R46" t="n">
-        <v>7041200</v>
+        <v>7041536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,11 +5311,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5939,7 +5939,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669057</v>
+        <v>127669063</v>
       </c>
       <c r="B53" t="n">
         <v>57661</v>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462115</v>
+        <v>462099</v>
       </c>
       <c r="R53" t="n">
-        <v>7041025</v>
+        <v>7041019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127669063</v>
+        <v>127669057</v>
       </c>
       <c r="B54" t="n">
         <v>57661</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462099</v>
+        <v>462115</v>
       </c>
       <c r="R54" t="n">
-        <v>7041019</v>
+        <v>7041025</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669054</v>
+        <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>57661</v>
+        <v>92027</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461774</v>
+        <v>462042</v>
       </c>
       <c r="R55" t="n">
-        <v>7041329</v>
+        <v>7041614</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6214,11 +6214,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6342,7 +6337,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B57" t="n">
         <v>57661</v>
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R57" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6417,7 +6412,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6444,32 +6439,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669046</v>
+        <v>127669071</v>
       </c>
       <c r="B58" t="n">
-        <v>92027</v>
+        <v>57661</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6479,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462042</v>
+        <v>461583</v>
       </c>
       <c r="R58" t="n">
-        <v>7041614</v>
+        <v>7041458</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6515,6 +6510,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669079</v>
+        <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461787</v>
+        <v>461891</v>
       </c>
       <c r="R15" t="n">
-        <v>7041311</v>
+        <v>7041546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R16" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,11 +2340,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669088</v>
+        <v>127669079</v>
       </c>
       <c r="B17" t="n">
-        <v>91348</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461891</v>
+        <v>461787</v>
       </c>
       <c r="R17" t="n">
-        <v>7041546</v>
+        <v>7041311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R18" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,6 +2534,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R19" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,6 +2636,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2697,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R20" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,11 +2738,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669060</v>
+        <v>127669084</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462105</v>
+        <v>461929</v>
       </c>
       <c r="R21" t="n">
-        <v>7040991</v>
+        <v>7041760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,11 +2835,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669056</v>
+        <v>127669073</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461996</v>
+        <v>461824</v>
       </c>
       <c r="R22" t="n">
-        <v>7041113</v>
+        <v>7041252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,11 +2932,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R23" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3065,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669076</v>
+        <v>127669060</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3066,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461956</v>
+        <v>462105</v>
       </c>
       <c r="R24" t="n">
-        <v>7041566</v>
+        <v>7040991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3126,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B30" t="n">
-        <v>91348</v>
+        <v>91326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R30" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>462009</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,11 +5005,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5031,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669064</v>
       </c>
       <c r="B44" t="n">
         <v>57661</v>
@@ -5071,10 +5066,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>462063</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5106,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5133,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669055</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5173,10 +5168,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>461992</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5208,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5240,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669085</v>
+        <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,21 +5246,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462009</v>
+        <v>461928</v>
       </c>
       <c r="R46" t="n">
-        <v>7041536</v>
+        <v>7041135</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,6 +5306,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B55" t="n">
-        <v>92027</v>
+        <v>91326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R55" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B56" t="n">
-        <v>91326</v>
+        <v>92027</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R56" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669088</v>
+        <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461891</v>
+        <v>461787</v>
       </c>
       <c r="R15" t="n">
-        <v>7041546</v>
+        <v>7041311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B16" t="n">
-        <v>91348</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R16" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,6 +2340,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669079</v>
+        <v>127669088</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2382,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461787</v>
+        <v>461891</v>
       </c>
       <c r="R17" t="n">
-        <v>7041311</v>
+        <v>7041546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R18" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,11 +2539,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R19" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,11 +2636,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,21 +2673,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2697,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R20" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,6 +2733,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R21" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669073</v>
+        <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461824</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>7041252</v>
+        <v>7041760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>80123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R23" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3058,7 +3058,7 @@
         <v>127669060</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127669081</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>127669065</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R29" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127669072</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127669070</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>91348</v>
+        <v>88735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R36" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>88733</v>
+        <v>91350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R37" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>91739</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4506,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B39" t="n">
-        <v>91737</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4604,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669094</v>
+        <v>127669059</v>
       </c>
       <c r="B40" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461551</v>
+        <v>462135</v>
       </c>
       <c r="R40" t="n">
-        <v>7041522</v>
+        <v>7040976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,6 +4704,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4730,10 +4735,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669059</v>
+        <v>127669053</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4765,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462135</v>
+        <v>461654</v>
       </c>
       <c r="R41" t="n">
-        <v>7040976</v>
+        <v>7041431</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4832,10 +4837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669053</v>
+        <v>127669094</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4843,21 +4848,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461654</v>
+        <v>461551</v>
       </c>
       <c r="R42" t="n">
-        <v>7041431</v>
+        <v>7041522</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,11 +4908,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4937,7 +4937,7 @@
         <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>127669064</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>127669055</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>127669068</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>127669067</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>127669069</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>127669063</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>127669057</v>
       </c>
       <c r="B54" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>127669075</v>
       </c>
       <c r="B55" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127669046</v>
       </c>
       <c r="B56" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>127669054</v>
       </c>
       <c r="B57" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>127669071</v>
       </c>
       <c r="B58" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669084</v>
+        <v>127669073</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>461824</v>
       </c>
       <c r="R22" t="n">
-        <v>7041760</v>
+        <v>7041252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669073</v>
+        <v>127669084</v>
       </c>
       <c r="B23" t="n">
-        <v>80123</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461824</v>
+        <v>461929</v>
       </c>
       <c r="R23" t="n">
-        <v>7041252</v>
+        <v>7041760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>88735</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R36" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>91350</v>
+        <v>88735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R37" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>91739</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,16 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R38" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>91739</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,21 +4551,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R39" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669059</v>
+        <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462135</v>
+        <v>461551</v>
       </c>
       <c r="R40" t="n">
-        <v>7040976</v>
+        <v>7041522</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,11 +4704,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4735,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669053</v>
+        <v>127669059</v>
       </c>
       <c r="B41" t="n">
         <v>57663</v>
@@ -4770,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461654</v>
+        <v>462135</v>
       </c>
       <c r="R41" t="n">
-        <v>7041431</v>
+        <v>7040976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4837,10 +4832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669094</v>
+        <v>127669053</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,21 +4843,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4872,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461551</v>
+        <v>461654</v>
       </c>
       <c r="R42" t="n">
-        <v>7041522</v>
+        <v>7041431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,6 +4903,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669085</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462009</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041536</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,6 +5005,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,7 +5036,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
         <v>57663</v>
@@ -5066,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5133,7 +5138,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669055</v>
+        <v>127669066</v>
       </c>
       <c r="B45" t="n">
         <v>57663</v>
@@ -5168,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461992</v>
+        <v>461928</v>
       </c>
       <c r="R45" t="n">
-        <v>7041200</v>
+        <v>7041135</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,7 +5213,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669066</v>
+        <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461928</v>
+        <v>462009</v>
       </c>
       <c r="R46" t="n">
-        <v>7041135</v>
+        <v>7041536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,11 +5311,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>462009</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,11 +5005,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5031,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669064</v>
       </c>
       <c r="B44" t="n">
         <v>57663</v>
@@ -5071,10 +5066,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>462063</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5106,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5133,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669055</v>
       </c>
       <c r="B45" t="n">
         <v>57663</v>
@@ -5173,10 +5168,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>461992</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5208,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5240,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669085</v>
+        <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,21 +5246,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462009</v>
+        <v>461928</v>
       </c>
       <c r="R46" t="n">
-        <v>7041536</v>
+        <v>7041135</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,6 +5306,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669079</v>
+        <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461787</v>
+        <v>461891</v>
       </c>
       <c r="R15" t="n">
-        <v>7041311</v>
+        <v>7041546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R16" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,11 +2340,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669088</v>
+        <v>127669095</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461891</v>
+        <v>462005</v>
       </c>
       <c r="R17" t="n">
-        <v>7041546</v>
+        <v>7041127</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669091</v>
+        <v>127669079</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462074</v>
+        <v>461787</v>
       </c>
       <c r="R18" t="n">
-        <v>7041005</v>
+        <v>7041311</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B21" t="n">
-        <v>91328</v>
+        <v>80123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R21" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669073</v>
+        <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>80123</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461824</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>7041252</v>
+        <v>7041760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R23" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B29" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R30" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>88735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R36" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>88735</v>
+        <v>91350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R37" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5408,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5445,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>91328</v>
+        <v>92029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R55" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B56" t="n">
-        <v>92029</v>
+        <v>91328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R56" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>127669091</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>127669079</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669073</v>
+        <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>80123</v>
+        <v>91334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461824</v>
+        <v>461956</v>
       </c>
       <c r="R21" t="n">
-        <v>7041252</v>
+        <v>7041566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669076</v>
+        <v>127669060</v>
       </c>
       <c r="B23" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461956</v>
+        <v>462105</v>
       </c>
       <c r="R23" t="n">
-        <v>7041566</v>
+        <v>7040991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,6 +3029,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669060</v>
+        <v>127669056</v>
       </c>
       <c r="B24" t="n">
         <v>57663</v>
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462105</v>
+        <v>461996</v>
       </c>
       <c r="R24" t="n">
-        <v>7040991</v>
+        <v>7041113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669056</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461996</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041113</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,7 +3262,7 @@
         <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127669081</v>
       </c>
       <c r="B27" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>91334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R29" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91328</v>
+        <v>91356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>88735</v>
+        <v>91356</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R36" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>91350</v>
+        <v>88741</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R37" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669069</v>
+        <v>127669063</v>
       </c>
       <c r="B52" t="n">
         <v>57663</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461820</v>
+        <v>462099</v>
       </c>
       <c r="R52" t="n">
-        <v>7041262</v>
+        <v>7041019</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669063</v>
+        <v>127669069</v>
       </c>
       <c r="B53" t="n">
         <v>57663</v>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462099</v>
+        <v>461820</v>
       </c>
       <c r="R53" t="n">
-        <v>7041019</v>
+        <v>7041262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B55" t="n">
-        <v>92029</v>
+        <v>91334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R55" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B56" t="n">
-        <v>91328</v>
+        <v>92035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R56" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669088</v>
+        <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461891</v>
+        <v>461787</v>
       </c>
       <c r="R15" t="n">
-        <v>7041546</v>
+        <v>7041311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669091</v>
+        <v>127669088</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462074</v>
+        <v>461891</v>
       </c>
       <c r="R16" t="n">
-        <v>7041005</v>
+        <v>7041546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R17" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,11 +2437,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669079</v>
+        <v>127669095</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461787</v>
+        <v>462005</v>
       </c>
       <c r="R18" t="n">
-        <v>7041311</v>
+        <v>7041127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,6 +2534,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,7 +2568,7 @@
         <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127669062</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B21" t="n">
-        <v>91334</v>
+        <v>80126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R21" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R22" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669084</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461929</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,11 +3029,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669056</v>
+        <v>127669060</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461996</v>
+        <v>462105</v>
       </c>
       <c r="R24" t="n">
-        <v>7041113</v>
+        <v>7040991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,7 +3262,7 @@
         <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669081</v>
+        <v>127669065</v>
       </c>
       <c r="B27" t="n">
-        <v>91334</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461655</v>
+        <v>462058</v>
       </c>
       <c r="R27" t="n">
-        <v>7041293</v>
+        <v>7041020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,6 +3427,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3453,10 +3458,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669065</v>
+        <v>127669081</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,21 +3469,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462058</v>
+        <v>461655</v>
       </c>
       <c r="R28" t="n">
-        <v>7041020</v>
+        <v>7041293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,11 +3529,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3558,7 +3558,7 @@
         <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127669072</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127669070</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>91356</v>
+        <v>88744</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R36" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>88741</v>
+        <v>91359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R37" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
         <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669094</v>
+        <v>127669059</v>
       </c>
       <c r="B40" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461551</v>
+        <v>462135</v>
       </c>
       <c r="R40" t="n">
-        <v>7041522</v>
+        <v>7040976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,6 +4704,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4730,10 +4735,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669059</v>
+        <v>127669094</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4741,21 +4746,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4765,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462135</v>
+        <v>461551</v>
       </c>
       <c r="R41" t="n">
-        <v>7040976</v>
+        <v>7041522</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4801,11 +4806,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,7 +4835,7 @@
         <v>127669053</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>127669064</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>127669055</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>127669068</v>
       </c>
       <c r="B50" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>127669067</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669063</v>
+        <v>127669069</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462099</v>
+        <v>461820</v>
       </c>
       <c r="R52" t="n">
-        <v>7041019</v>
+        <v>7041262</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669069</v>
+        <v>127669063</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461820</v>
+        <v>462099</v>
       </c>
       <c r="R53" t="n">
-        <v>7041262</v>
+        <v>7041019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6044,7 +6044,7 @@
         <v>127669057</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>91334</v>
+        <v>92038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R55" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669046</v>
+        <v>127669054</v>
       </c>
       <c r="B56" t="n">
-        <v>92035</v>
+        <v>57666</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462042</v>
+        <v>461774</v>
       </c>
       <c r="R56" t="n">
-        <v>7041614</v>
+        <v>7041329</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,6 +6311,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6337,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669054</v>
+        <v>127669075</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6348,21 +6353,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461774</v>
+        <v>461962</v>
       </c>
       <c r="R57" t="n">
-        <v>7041329</v>
+        <v>7041573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,11 +6413,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6442,7 +6442,7 @@
         <v>127669071</v>
       </c>
       <c r="B58" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669088</v>
+        <v>127669095</v>
       </c>
       <c r="B16" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461891</v>
+        <v>462005</v>
       </c>
       <c r="R16" t="n">
-        <v>7041546</v>
+        <v>7041127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,6 +2340,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669091</v>
+        <v>127669088</v>
       </c>
       <c r="B17" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462074</v>
+        <v>461891</v>
       </c>
       <c r="R17" t="n">
-        <v>7041005</v>
+        <v>7041546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R18" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,11 +2539,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,7 +2568,7 @@
         <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127669062</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669073</v>
+        <v>127669060</v>
       </c>
       <c r="B21" t="n">
-        <v>80126</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461824</v>
+        <v>462105</v>
       </c>
       <c r="R21" t="n">
-        <v>7041252</v>
+        <v>7040991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,6 +2835,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,10 +2866,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669076</v>
+        <v>127669056</v>
       </c>
       <c r="B22" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2877,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461956</v>
+        <v>461996</v>
       </c>
       <c r="R22" t="n">
-        <v>7041566</v>
+        <v>7041113</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,6 +2937,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B23" t="n">
-        <v>91359</v>
+        <v>91345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R23" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669060</v>
+        <v>127669073</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462105</v>
+        <v>461824</v>
       </c>
       <c r="R24" t="n">
-        <v>7040991</v>
+        <v>7041252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669056</v>
+        <v>127669084</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461996</v>
+        <v>461929</v>
       </c>
       <c r="R25" t="n">
-        <v>7041113</v>
+        <v>7041760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,7 +3262,7 @@
         <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669065</v>
+        <v>127669081</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462058</v>
+        <v>461655</v>
       </c>
       <c r="R27" t="n">
-        <v>7041020</v>
+        <v>7041293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,11 +3427,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669081</v>
+        <v>127669065</v>
       </c>
       <c r="B28" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,21 +3464,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461655</v>
+        <v>462058</v>
       </c>
       <c r="R28" t="n">
-        <v>7041293</v>
+        <v>7041020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,6 +3524,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3558,7 +3558,7 @@
         <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127669072</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127669070</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91748</v>
+        <v>91756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669059</v>
+        <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462135</v>
+        <v>461551</v>
       </c>
       <c r="R40" t="n">
-        <v>7040976</v>
+        <v>7041522</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,11 +4704,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4735,10 +4730,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669094</v>
+        <v>127669059</v>
       </c>
       <c r="B41" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4746,21 +4741,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4770,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461551</v>
+        <v>462135</v>
       </c>
       <c r="R41" t="n">
-        <v>7041522</v>
+        <v>7040976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4806,6 +4801,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,7 +4835,7 @@
         <v>127669053</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669085</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462009</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041536</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,6 +5005,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,10 +5036,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5066,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5133,10 +5138,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669055</v>
+        <v>127669066</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5168,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461992</v>
+        <v>461928</v>
       </c>
       <c r="R45" t="n">
-        <v>7041200</v>
+        <v>7041135</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,7 +5213,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669066</v>
+        <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461928</v>
+        <v>462009</v>
       </c>
       <c r="R46" t="n">
-        <v>7041135</v>
+        <v>7041536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,11 +5311,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B47" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5408,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5445,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>127669068</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>127669067</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669069</v>
+        <v>127669057</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461820</v>
+        <v>462115</v>
       </c>
       <c r="R52" t="n">
-        <v>7041262</v>
+        <v>7041025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669063</v>
+        <v>127669069</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462099</v>
+        <v>461820</v>
       </c>
       <c r="R53" t="n">
-        <v>7041019</v>
+        <v>7041262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127669057</v>
+        <v>127669063</v>
       </c>
       <c r="B54" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462115</v>
+        <v>462099</v>
       </c>
       <c r="R54" t="n">
-        <v>7041025</v>
+        <v>7041019</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,7 +6146,7 @@
         <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669054</v>
+        <v>127669075</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461774</v>
+        <v>461962</v>
       </c>
       <c r="R56" t="n">
-        <v>7041329</v>
+        <v>7041573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,11 +6311,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6342,10 +6337,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669075</v>
+        <v>127669071</v>
       </c>
       <c r="B57" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,21 +6348,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461962</v>
+        <v>461583</v>
       </c>
       <c r="R57" t="n">
-        <v>7041573</v>
+        <v>7041458</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6413,6 +6408,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B58" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R58" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669079</v>
+        <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461787</v>
+        <v>461891</v>
       </c>
       <c r="R15" t="n">
-        <v>7041311</v>
+        <v>7041546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R16" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,11 +2340,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669088</v>
+        <v>127669079</v>
       </c>
       <c r="B17" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461891</v>
+        <v>461787</v>
       </c>
       <c r="R17" t="n">
-        <v>7041546</v>
+        <v>7041311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B18" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R18" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,6 +2534,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,7 +2568,7 @@
         <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669060</v>
+        <v>127669084</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462105</v>
+        <v>461929</v>
       </c>
       <c r="R21" t="n">
-        <v>7040991</v>
+        <v>7041760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,11 +2835,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669076</v>
+        <v>127669060</v>
       </c>
       <c r="B23" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461956</v>
+        <v>462105</v>
       </c>
       <c r="R23" t="n">
-        <v>7041566</v>
+        <v>7040991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669073</v>
+        <v>127669076</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>91346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461824</v>
+        <v>461956</v>
       </c>
       <c r="R24" t="n">
-        <v>7041252</v>
+        <v>7041566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669084</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>91367</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461929</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041760</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
         <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127669081</v>
       </c>
       <c r="B27" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B29" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B30" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R30" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91757</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4506,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B39" t="n">
-        <v>91756</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4604,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5036,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669066</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>461928</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041135</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5138,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669064</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>462063</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
         <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669057</v>
+        <v>127669063</v>
       </c>
       <c r="B52" t="n">
         <v>57672</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462115</v>
+        <v>462099</v>
       </c>
       <c r="R52" t="n">
-        <v>7041025</v>
+        <v>7041019</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669069</v>
+        <v>127669057</v>
       </c>
       <c r="B53" t="n">
         <v>57672</v>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461820</v>
+        <v>462115</v>
       </c>
       <c r="R53" t="n">
-        <v>7041262</v>
+        <v>7041025</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127669063</v>
+        <v>127669069</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462099</v>
+        <v>461820</v>
       </c>
       <c r="R54" t="n">
-        <v>7041019</v>
+        <v>7041262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,7 +6146,7 @@
         <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127669075</v>
       </c>
       <c r="B56" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R57" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669054</v>
+        <v>127669071</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461774</v>
+        <v>461583</v>
       </c>
       <c r="R58" t="n">
-        <v>7041329</v>
+        <v>7041458</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669088</v>
+        <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461891</v>
+        <v>461787</v>
       </c>
       <c r="R15" t="n">
-        <v>7041546</v>
+        <v>7041311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669091</v>
+        <v>127669088</v>
       </c>
       <c r="B16" t="n">
         <v>91368</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462074</v>
+        <v>461891</v>
       </c>
       <c r="R16" t="n">
-        <v>7041005</v>
+        <v>7041546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669079</v>
+        <v>127669091</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461787</v>
+        <v>462074</v>
       </c>
       <c r="R17" t="n">
-        <v>7041311</v>
+        <v>7041005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R21" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669056</v>
+        <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461996</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>7041113</v>
+        <v>7041760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,11 +2932,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669073</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461824</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3029,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669076</v>
+        <v>127669060</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3066,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461956</v>
+        <v>462105</v>
       </c>
       <c r="R24" t="n">
-        <v>7041566</v>
+        <v>7040991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3126,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669080</v>
+        <v>127669065</v>
       </c>
       <c r="B26" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461710</v>
+        <v>462058</v>
       </c>
       <c r="R26" t="n">
-        <v>7041300</v>
+        <v>7041020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3330,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3356,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669081</v>
+        <v>127669080</v>
       </c>
       <c r="B27" t="n">
         <v>91346</v>
@@ -3391,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461655</v>
+        <v>461710</v>
       </c>
       <c r="R27" t="n">
-        <v>7041293</v>
+        <v>7041300</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,10 +3458,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669065</v>
+        <v>127669081</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,21 +3469,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462058</v>
+        <v>461655</v>
       </c>
       <c r="R28" t="n">
-        <v>7041020</v>
+        <v>7041293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,11 +3529,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R29" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>88753</v>
+        <v>91368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R36" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>91368</v>
+        <v>88753</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R37" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>91757</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,16 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R38" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,21 +4551,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R39" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669059</v>
+        <v>127669053</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462135</v>
+        <v>461654</v>
       </c>
       <c r="R41" t="n">
-        <v>7040976</v>
+        <v>7041431</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669053</v>
+        <v>127669059</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461654</v>
+        <v>462135</v>
       </c>
       <c r="R42" t="n">
-        <v>7041431</v>
+        <v>7040976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669055</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461992</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041200</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5036,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669066</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461928</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041135</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5138,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669064</v>
+        <v>127669066</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462063</v>
+        <v>461928</v>
       </c>
       <c r="R45" t="n">
-        <v>7041008</v>
+        <v>7041135</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669063</v>
+        <v>127669069</v>
       </c>
       <c r="B52" t="n">
         <v>57672</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462099</v>
+        <v>461820</v>
       </c>
       <c r="R52" t="n">
-        <v>7041019</v>
+        <v>7041262</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669057</v>
+        <v>127669063</v>
       </c>
       <c r="B53" t="n">
         <v>57672</v>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462115</v>
+        <v>462099</v>
       </c>
       <c r="R53" t="n">
-        <v>7041025</v>
+        <v>7041019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127669069</v>
+        <v>127669057</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461820</v>
+        <v>462115</v>
       </c>
       <c r="R54" t="n">
-        <v>7041262</v>
+        <v>7041025</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B55" t="n">
-        <v>92047</v>
+        <v>91346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R55" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B56" t="n">
-        <v>91346</v>
+        <v>92047</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R56" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669054</v>
+        <v>127669071</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461774</v>
+        <v>461583</v>
       </c>
       <c r="R57" t="n">
-        <v>7041329</v>
+        <v>7041458</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R58" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>127669088</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B17" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R17" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,6 +2437,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669095</v>
+        <v>127669091</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>91369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462005</v>
+        <v>462074</v>
       </c>
       <c r="R18" t="n">
-        <v>7041127</v>
+        <v>7041005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,11 +2539,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R19" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,6 +2636,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2697,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R20" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,11 +2738,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,7 +2767,7 @@
         <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669065</v>
+        <v>127669080</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462058</v>
+        <v>461710</v>
       </c>
       <c r="R26" t="n">
-        <v>7041020</v>
+        <v>7041300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669080</v>
+        <v>127669081</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461710</v>
+        <v>461655</v>
       </c>
       <c r="R27" t="n">
-        <v>7041300</v>
+        <v>7041293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669081</v>
+        <v>127669065</v>
       </c>
       <c r="B28" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,21 +3464,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461655</v>
+        <v>462058</v>
       </c>
       <c r="R28" t="n">
-        <v>7041293</v>
+        <v>7041020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,6 +3524,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B29" t="n">
-        <v>91346</v>
+        <v>91369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B30" t="n">
-        <v>91368</v>
+        <v>91347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R30" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669082</v>
+        <v>127669090</v>
       </c>
       <c r="B31" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461773</v>
+        <v>461887</v>
       </c>
       <c r="R31" t="n">
-        <v>7041572</v>
+        <v>7041257</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127669090</v>
+        <v>127669082</v>
       </c>
       <c r="B32" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461887</v>
+        <v>461773</v>
       </c>
       <c r="R32" t="n">
-        <v>7041257</v>
+        <v>7041572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669094</v>
+        <v>127669059</v>
       </c>
       <c r="B40" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461551</v>
+        <v>462135</v>
       </c>
       <c r="R40" t="n">
-        <v>7041522</v>
+        <v>7040976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,6 +4704,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4832,10 +4837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669059</v>
+        <v>127669094</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4843,21 +4848,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462135</v>
+        <v>461551</v>
       </c>
       <c r="R42" t="n">
-        <v>7040976</v>
+        <v>7041522</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,11 +4908,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>462009</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,11 +5005,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5031,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669064</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5071,10 +5066,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>462063</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5106,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5133,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669055</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5173,10 +5168,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>461992</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5208,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5240,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669085</v>
+        <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,21 +5246,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462009</v>
+        <v>461928</v>
       </c>
       <c r="R46" t="n">
-        <v>7041536</v>
+        <v>7041135</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,6 +5306,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5340,7 +5340,7 @@
         <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B55" t="n">
-        <v>91346</v>
+        <v>92048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R55" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B56" t="n">
-        <v>92047</v>
+        <v>91347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R56" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R57" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669054</v>
+        <v>127669071</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461774</v>
+        <v>461583</v>
       </c>
       <c r="R58" t="n">
-        <v>7041329</v>
+        <v>7041458</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>127669079</v>
       </c>
       <c r="B15" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669088</v>
+        <v>127669095</v>
       </c>
       <c r="B16" t="n">
-        <v>91369</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461891</v>
+        <v>462005</v>
       </c>
       <c r="R16" t="n">
-        <v>7041546</v>
+        <v>7041127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,6 +2340,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669095</v>
+        <v>127669088</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2382,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462005</v>
+        <v>461891</v>
       </c>
       <c r="R17" t="n">
-        <v>7041127</v>
+        <v>7041546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,7 +2471,7 @@
         <v>127669091</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>127669077</v>
       </c>
       <c r="B20" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669076</v>
+        <v>127669084</v>
       </c>
       <c r="B21" t="n">
-        <v>91347</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R21" t="n">
-        <v>7041566</v>
+        <v>7041760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R22" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669073</v>
+        <v>127669060</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461824</v>
+        <v>462105</v>
       </c>
       <c r="R23" t="n">
-        <v>7041252</v>
+        <v>7040991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,6 +3029,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669060</v>
+        <v>127669056</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462105</v>
+        <v>461996</v>
       </c>
       <c r="R24" t="n">
-        <v>7040991</v>
+        <v>7041113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669056</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461996</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041113</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669080</v>
+        <v>127669081</v>
       </c>
       <c r="B26" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461710</v>
+        <v>461655</v>
       </c>
       <c r="R26" t="n">
-        <v>7041300</v>
+        <v>7041293</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669081</v>
+        <v>127669080</v>
       </c>
       <c r="B27" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461655</v>
+        <v>461710</v>
       </c>
       <c r="R27" t="n">
-        <v>7041293</v>
+        <v>7041300</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669086</v>
+        <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91369</v>
+        <v>91348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461915</v>
+        <v>461868</v>
       </c>
       <c r="R29" t="n">
-        <v>7041539</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669078</v>
+        <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91347</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461868</v>
+        <v>461915</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041539</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669090</v>
+        <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461887</v>
+        <v>461773</v>
       </c>
       <c r="R31" t="n">
-        <v>7041257</v>
+        <v>7041572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127669082</v>
+        <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461773</v>
+        <v>461887</v>
       </c>
       <c r="R32" t="n">
-        <v>7041572</v>
+        <v>7041257</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669059</v>
+        <v>127669094</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462135</v>
+        <v>461551</v>
       </c>
       <c r="R40" t="n">
-        <v>7040976</v>
+        <v>7041522</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,11 +4704,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4735,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669053</v>
+        <v>127669059</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4770,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461654</v>
+        <v>462135</v>
       </c>
       <c r="R41" t="n">
-        <v>7041431</v>
+        <v>7040976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4837,10 +4832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669094</v>
+        <v>127669053</v>
       </c>
       <c r="B42" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,21 +4843,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4872,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461551</v>
+        <v>461654</v>
       </c>
       <c r="R42" t="n">
-        <v>7041522</v>
+        <v>7041431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,6 +4903,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669085</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462009</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041536</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,6 +5005,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,7 +5036,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5066,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5133,7 +5138,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669055</v>
+        <v>127669066</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5168,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461992</v>
+        <v>461928</v>
       </c>
       <c r="R45" t="n">
-        <v>7041200</v>
+        <v>7041135</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,7 +5213,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669066</v>
+        <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461928</v>
+        <v>462009</v>
       </c>
       <c r="R46" t="n">
-        <v>7041135</v>
+        <v>7041536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,11 +5311,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5340,7 +5340,7 @@
         <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6143,32 +6143,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669046</v>
+        <v>127669075</v>
       </c>
       <c r="B55" t="n">
-        <v>92048</v>
+        <v>91348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462042</v>
+        <v>461962</v>
       </c>
       <c r="R55" t="n">
-        <v>7041614</v>
+        <v>7041573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669075</v>
+        <v>127669071</v>
       </c>
       <c r="B56" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461962</v>
+        <v>461583</v>
       </c>
       <c r="R56" t="n">
-        <v>7041573</v>
+        <v>7041458</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,6 +6311,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6337,32 +6342,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669054</v>
+        <v>127669046</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461774</v>
+        <v>462042</v>
       </c>
       <c r="R57" t="n">
-        <v>7041329</v>
+        <v>7041614</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,11 +6413,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669071</v>
+        <v>127669054</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461583</v>
+        <v>461774</v>
       </c>
       <c r="R58" t="n">
-        <v>7041458</v>
+        <v>7041329</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669095</v>
+        <v>127669088</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462005</v>
+        <v>461891</v>
       </c>
       <c r="R16" t="n">
-        <v>7041127</v>
+        <v>7041546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,11 +2340,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,7 +2366,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669088</v>
+        <v>127669091</v>
       </c>
       <c r="B17" t="n">
         <v>91370</v>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461891</v>
+        <v>462074</v>
       </c>
       <c r="R17" t="n">
-        <v>7041546</v>
+        <v>7041005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R18" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,6 +2534,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R21" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669076</v>
+        <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>7041566</v>
+        <v>7041760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669073</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461824</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,11 +3029,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3055,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669056</v>
+        <v>127669060</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461996</v>
+        <v>462105</v>
       </c>
       <c r="R24" t="n">
-        <v>7041113</v>
+        <v>7040991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669081</v>
+        <v>127669065</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461655</v>
+        <v>462058</v>
       </c>
       <c r="R26" t="n">
-        <v>7041293</v>
+        <v>7041020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3330,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,10 +3458,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669065</v>
+        <v>127669081</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,21 +3469,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462058</v>
+        <v>461655</v>
       </c>
       <c r="R28" t="n">
-        <v>7041020</v>
+        <v>7041293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,11 +3529,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669082</v>
+        <v>127669072</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461773</v>
+        <v>461817</v>
       </c>
       <c r="R31" t="n">
-        <v>7041572</v>
+        <v>7041252</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,6 +3820,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3943,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669072</v>
+        <v>127669082</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,21 +3959,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3978,10 +3983,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461817</v>
+        <v>461773</v>
       </c>
       <c r="R33" t="n">
-        <v>7041252</v>
+        <v>7041572</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4014,11 +4019,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4506,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4604,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669094</v>
+        <v>127669059</v>
       </c>
       <c r="B40" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461551</v>
+        <v>462135</v>
       </c>
       <c r="R40" t="n">
-        <v>7041522</v>
+        <v>7040976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,6 +4704,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4730,7 +4735,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669059</v>
+        <v>127669053</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4765,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462135</v>
+        <v>461654</v>
       </c>
       <c r="R41" t="n">
-        <v>7040976</v>
+        <v>7041431</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4832,10 +4837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669053</v>
+        <v>127669094</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4843,21 +4848,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461654</v>
+        <v>461551</v>
       </c>
       <c r="R42" t="n">
-        <v>7041431</v>
+        <v>7041522</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,11 +4908,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669085</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>462009</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,11 +5005,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,7 +5031,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669064</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5071,10 +5066,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>462063</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5106,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5138,7 +5133,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669055</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5173,10 +5168,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>461992</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5208,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5240,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669085</v>
+        <v>127669066</v>
       </c>
       <c r="B46" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,21 +5246,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462009</v>
+        <v>461928</v>
       </c>
       <c r="R46" t="n">
-        <v>7041536</v>
+        <v>7041135</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,6 +5306,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6240,32 +6240,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669071</v>
+        <v>127669046</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461583</v>
+        <v>462042</v>
       </c>
       <c r="R56" t="n">
-        <v>7041458</v>
+        <v>7041614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,11 +6311,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6342,32 +6337,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669046</v>
+        <v>127669054</v>
       </c>
       <c r="B57" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462042</v>
+        <v>461774</v>
       </c>
       <c r="R57" t="n">
-        <v>7041614</v>
+        <v>7041329</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6413,6 +6408,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669054</v>
+        <v>127669071</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461774</v>
+        <v>461583</v>
       </c>
       <c r="R58" t="n">
-        <v>7041329</v>
+        <v>7041458</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R21" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669084</v>
+        <v>127669076</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R22" t="n">
-        <v>7041760</v>
+        <v>7041566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669073</v>
+        <v>127669084</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461824</v>
+        <v>461929</v>
       </c>
       <c r="R23" t="n">
-        <v>7041252</v>
+        <v>7041760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B36" t="n">
-        <v>91370</v>
+        <v>88755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R36" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B37" t="n">
-        <v>88755</v>
+        <v>91370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R37" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,16 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R38" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,21 +4551,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R39" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5408,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5445,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669073</v>
+        <v>127669076</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461824</v>
+        <v>461956</v>
       </c>
       <c r="R21" t="n">
-        <v>7041252</v>
+        <v>7041566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669076</v>
+        <v>127669084</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>7041566</v>
+        <v>7041760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669084</v>
+        <v>127669073</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461929</v>
+        <v>461824</v>
       </c>
       <c r="R23" t="n">
-        <v>7041760</v>
+        <v>7041252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4506,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4604,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,16 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R38" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,21 +4551,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R39" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R19" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,11 +2636,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,21 +2673,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2697,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R20" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,6 +2733,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669073</v>
+        <v>127669060</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461824</v>
+        <v>462105</v>
       </c>
       <c r="R23" t="n">
-        <v>7041252</v>
+        <v>7040991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,6 +3029,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669060</v>
+        <v>127669056</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462105</v>
+        <v>461996</v>
       </c>
       <c r="R24" t="n">
-        <v>7040991</v>
+        <v>7041113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669056</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461996</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041113</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4506,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4604,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5408,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5445,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669079</v>
+        <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461787</v>
+        <v>461891</v>
       </c>
       <c r="R15" t="n">
-        <v>7041311</v>
+        <v>7041546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669088</v>
+        <v>127669091</v>
       </c>
       <c r="B16" t="n">
         <v>91370</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461891</v>
+        <v>462074</v>
       </c>
       <c r="R16" t="n">
-        <v>7041546</v>
+        <v>7041005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669091</v>
+        <v>127669095</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462074</v>
+        <v>462005</v>
       </c>
       <c r="R17" t="n">
-        <v>7041005</v>
+        <v>7041127</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,6 +2437,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669095</v>
+        <v>127669079</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462005</v>
+        <v>461787</v>
       </c>
       <c r="R18" t="n">
-        <v>7041127</v>
+        <v>7041311</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,11 +2539,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669073</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461824</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,11 +3029,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3055,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669056</v>
+        <v>127669060</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461996</v>
+        <v>462105</v>
       </c>
       <c r="R24" t="n">
-        <v>7041113</v>
+        <v>7040991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>127669056</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461996</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4244,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669097</v>
+        <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>88755</v>
+        <v>91370</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461933</v>
+        <v>461855</v>
       </c>
       <c r="R36" t="n">
-        <v>7041131</v>
+        <v>7041550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669089</v>
+        <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>91370</v>
+        <v>88755</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461855</v>
+        <v>461933</v>
       </c>
       <c r="R37" t="n">
-        <v>7041550</v>
+        <v>7041131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669074</v>
+        <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,16 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461699</v>
+        <v>462095</v>
       </c>
       <c r="R38" t="n">
-        <v>7041298</v>
+        <v>7041036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669096</v>
+        <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,21 +4551,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462095</v>
+        <v>461699</v>
       </c>
       <c r="R39" t="n">
-        <v>7041036</v>
+        <v>7041298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669077</v>
+        <v>127669062</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461872</v>
+        <v>462111</v>
       </c>
       <c r="R19" t="n">
-        <v>7041556</v>
+        <v>7041002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,6 +2636,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669062</v>
+        <v>127669077</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2697,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462111</v>
+        <v>461872</v>
       </c>
       <c r="R20" t="n">
-        <v>7041002</v>
+        <v>7041556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,11 +2738,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669073</v>
+        <v>127669060</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461824</v>
+        <v>462105</v>
       </c>
       <c r="R23" t="n">
-        <v>7041252</v>
+        <v>7040991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,6 +3029,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669060</v>
+        <v>127669056</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462105</v>
+        <v>461996</v>
       </c>
       <c r="R24" t="n">
-        <v>7040991</v>
+        <v>7041113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669056</v>
+        <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461996</v>
+        <v>461824</v>
       </c>
       <c r="R25" t="n">
-        <v>7041113</v>
+        <v>7041252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5408,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5445,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,11 +5510,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>127669088</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>127669091</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>127669095</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>127669079</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>127669062</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>127669077</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669076</v>
+        <v>127669084</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R21" t="n">
-        <v>7041566</v>
+        <v>7041760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669084</v>
+        <v>127669060</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>462105</v>
       </c>
       <c r="R22" t="n">
-        <v>7041760</v>
+        <v>7040991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,6 +2932,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669060</v>
+        <v>127669056</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462105</v>
+        <v>461996</v>
       </c>
       <c r="R23" t="n">
-        <v>7040991</v>
+        <v>7041113</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +3038,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669056</v>
+        <v>127669076</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461996</v>
+        <v>461956</v>
       </c>
       <c r="R24" t="n">
-        <v>7041113</v>
+        <v>7041566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,7 +3165,7 @@
         <v>127669073</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127669065</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>127669080</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>127669081</v>
       </c>
       <c r="B28" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>127669078</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>127669086</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669072</v>
+        <v>127669082</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461817</v>
+        <v>461773</v>
       </c>
       <c r="R31" t="n">
-        <v>7041252</v>
+        <v>7041572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,11 +3820,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,7 +3849,7 @@
         <v>127669090</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,10 +3943,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669082</v>
+        <v>127669072</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3959,21 +3954,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3983,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461773</v>
+        <v>461817</v>
       </c>
       <c r="R33" t="n">
-        <v>7041572</v>
+        <v>7041252</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4019,6 +4014,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,7 +4048,7 @@
         <v>127669083</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127669070</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127669089</v>
       </c>
       <c r="B36" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127669097</v>
       </c>
       <c r="B37" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>127669096</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127669074</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>91767</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>127669059</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>127669053</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>127669094</v>
       </c>
       <c r="B42" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669085</v>
+        <v>127669064</v>
       </c>
       <c r="B43" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462009</v>
+        <v>462063</v>
       </c>
       <c r="R43" t="n">
-        <v>7041536</v>
+        <v>7041008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,6 +5005,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,10 +5036,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669064</v>
+        <v>127669055</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5066,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462063</v>
+        <v>461992</v>
       </c>
       <c r="R44" t="n">
-        <v>7041008</v>
+        <v>7041200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5133,10 +5138,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669055</v>
+        <v>127669066</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5168,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461992</v>
+        <v>461928</v>
       </c>
       <c r="R45" t="n">
-        <v>7041200</v>
+        <v>7041135</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,7 +5213,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669066</v>
+        <v>127669085</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461928</v>
+        <v>462009</v>
       </c>
       <c r="R46" t="n">
-        <v>7041135</v>
+        <v>7041536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,11 +5311,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669058</v>
+        <v>127669093</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462135</v>
+        <v>461799</v>
       </c>
       <c r="R47" t="n">
-        <v>7040973</v>
+        <v>7041221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,11 +5408,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669093</v>
+        <v>127669058</v>
       </c>
       <c r="B48" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>462135</v>
       </c>
       <c r="R48" t="n">
-        <v>7041221</v>
+        <v>7040973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,6 +5505,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5539,7 +5539,7 @@
         <v>127669087</v>
       </c>
       <c r="B49" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>127669068</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>127669067</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>127669069</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>127669063</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>127669057</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669075</v>
+        <v>127669054</v>
       </c>
       <c r="B55" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461962</v>
+        <v>461774</v>
       </c>
       <c r="R55" t="n">
-        <v>7041573</v>
+        <v>7041329</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6214,6 +6214,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6240,32 +6245,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669046</v>
+        <v>127669071</v>
       </c>
       <c r="B56" t="n">
-        <v>92049</v>
+        <v>57673</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6275,10 +6280,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462042</v>
+        <v>461583</v>
       </c>
       <c r="R56" t="n">
-        <v>7041614</v>
+        <v>7041458</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,6 +6316,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6337,10 +6347,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669054</v>
+        <v>127669075</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6348,21 +6358,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6372,10 +6382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461774</v>
+        <v>461962</v>
       </c>
       <c r="R57" t="n">
-        <v>7041329</v>
+        <v>7041573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,11 +6418,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6439,32 +6444,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669071</v>
+        <v>127669046</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6474,10 +6479,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461583</v>
+        <v>462042</v>
       </c>
       <c r="R58" t="n">
-        <v>7041458</v>
+        <v>7041614</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,11 +6515,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6143,7 +6143,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127669054</v>
+        <v>127669071</v>
       </c>
       <c r="B55" t="n">
         <v>57673</v>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461774</v>
+        <v>461583</v>
       </c>
       <c r="R55" t="n">
-        <v>7041329</v>
+        <v>7041458</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6245,10 +6245,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127669071</v>
+        <v>127669075</v>
       </c>
       <c r="B56" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461583</v>
+        <v>461962</v>
       </c>
       <c r="R56" t="n">
-        <v>7041458</v>
+        <v>7041573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6316,11 +6316,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6347,32 +6342,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669075</v>
+        <v>127669046</v>
       </c>
       <c r="B57" t="n">
-        <v>91356</v>
+        <v>92057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6382,10 +6377,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461962</v>
+        <v>462042</v>
       </c>
       <c r="R57" t="n">
-        <v>7041573</v>
+        <v>7041614</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6441,103 +6436,6 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>127669046</v>
-      </c>
-      <c r="B58" t="n">
-        <v>92057</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Bredbyn S, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>462042</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7041614</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102632572</v>
+        <v>102631781</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461878.4550593058</v>
+        <v>461901</v>
       </c>
       <c r="R2" t="n">
-        <v>7041552.433260036</v>
+        <v>7041524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102632284</v>
+        <v>127669097</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,48 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461885.9495161559</v>
+        <v>461933</v>
       </c>
       <c r="R3" t="n">
-        <v>7041655.519728451</v>
+        <v>7041131</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,27 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102631781</v>
+        <v>102632889</v>
       </c>
       <c r="B4" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461900.4729946476</v>
+        <v>461829</v>
       </c>
       <c r="R4" t="n">
-        <v>7041523.583794649</v>
+        <v>7041551</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +939,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102632889</v>
+        <v>127669075</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,20 +997,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461829.2371600438</v>
+        <v>461962</v>
       </c>
       <c r="R5" t="n">
-        <v>7041550.789072232</v>
+        <v>7041573</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1033,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,67 +1053,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102631971</v>
+        <v>127669076</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461882.3836461503</v>
+        <v>461956</v>
       </c>
       <c r="R6" t="n">
-        <v>7041544.346434344</v>
+        <v>7041566</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1130,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,27 +1150,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102632603</v>
+        <v>127669077</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,48 +1173,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461841.0459716322</v>
+        <v>461872</v>
       </c>
       <c r="R7" t="n">
-        <v>7041565.833977166</v>
+        <v>7041556</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,27 +1227,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,67 +1247,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102632640</v>
+        <v>127669078</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461837.0533436034</v>
+        <v>461868</v>
       </c>
       <c r="R8" t="n">
-        <v>7041568.561715186</v>
+        <v>7041553</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1324,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,27 +1344,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102633167</v>
+        <v>127669079</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,38 +1367,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461787.1019236122</v>
+        <v>461787</v>
       </c>
       <c r="R9" t="n">
-        <v>7041580.326608213</v>
+        <v>7041311</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1421,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,66 +1441,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102632314</v>
+        <v>127669080</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461890.8176240163</v>
+        <v>461710</v>
       </c>
       <c r="R10" t="n">
-        <v>7041576.40479657</v>
+        <v>7041300</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,22 +1518,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,27 +1538,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102632948</v>
+        <v>127669081</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,38 +1561,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461829.2371600438</v>
+        <v>461655</v>
       </c>
       <c r="R11" t="n">
-        <v>7041550.789072232</v>
+        <v>7041293</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,22 +1615,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,27 +1635,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102631814</v>
+        <v>102633167</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,21 +1658,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,10 +1683,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461900.4729946476</v>
+        <v>461787</v>
       </c>
       <c r="R12" t="n">
-        <v>7041523.583794649</v>
+        <v>7041580</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1906,19 +1716,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,15 +1745,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102632530</v>
+        <v>127669046</v>
       </c>
       <c r="B13" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,38 +1756,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bredbyn 2:1, Jmt</t>
+          <t>Bredbyn S, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461878.4550593058</v>
+        <v>462042</v>
       </c>
       <c r="R13" t="n">
-        <v>7041552.433260036</v>
+        <v>7041614</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,22 +1810,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,27 +1830,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102632317</v>
+        <v>102632530</v>
       </c>
       <c r="B14" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,36 +1853,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461890.8176240163</v>
+        <v>461878</v>
       </c>
       <c r="R14" t="n">
-        <v>7041576.40479657</v>
+        <v>7041552</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,19 +1911,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669088</v>
+        <v>102631714</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>93215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,37 +1951,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461891</v>
+        <v>461977</v>
       </c>
       <c r="R15" t="n">
-        <v>7041546</v>
+        <v>7041512</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2237,12 +2006,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I vägkanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,60 +2031,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669091</v>
+        <v>102632314</v>
       </c>
       <c r="B16" t="n">
-        <v>91378</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462074</v>
+        <v>461891</v>
       </c>
       <c r="R16" t="n">
-        <v>7041005</v>
+        <v>7041577</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,12 +2109,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,26 +2129,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669095</v>
+        <v>101731740</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2395,19 +2170,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Sjöarsjövägen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462005</v>
+        <v>461607</v>
       </c>
       <c r="R17" t="n">
-        <v>7041127</v>
+        <v>7041520</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,17 +2207,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,60 +2227,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669079</v>
+        <v>102632572</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461787</v>
+        <v>461878</v>
       </c>
       <c r="R18" t="n">
-        <v>7041311</v>
+        <v>7041552</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,12 +2305,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,60 +2325,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669062</v>
+        <v>102632948</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462111</v>
+        <v>461829</v>
       </c>
       <c r="R19" t="n">
-        <v>7041002</v>
+        <v>7041551</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,17 +2403,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,60 +2423,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669077</v>
+        <v>102633447</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461872</v>
+        <v>461741</v>
       </c>
       <c r="R20" t="n">
-        <v>7041556</v>
+        <v>7041627</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,12 +2501,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,44 +2521,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669084</v>
+        <v>127669095</v>
       </c>
       <c r="B21" t="n">
-        <v>91378</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>462005</v>
       </c>
       <c r="R21" t="n">
-        <v>7041760</v>
+        <v>7041127</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669060</v>
+        <v>127669096</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462105</v>
+        <v>462095</v>
       </c>
       <c r="R22" t="n">
-        <v>7040991</v>
+        <v>7041036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2710,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669056</v>
+        <v>102633444</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,37 +2748,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461996</v>
+        <v>461741</v>
       </c>
       <c r="R23" t="n">
-        <v>7041113</v>
+        <v>7041627</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3028,17 +2803,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,22 +2823,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669076</v>
+        <v>127669073</v>
       </c>
       <c r="B24" t="n">
-        <v>91356</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +2846,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461956</v>
+        <v>461824</v>
       </c>
       <c r="R24" t="n">
-        <v>7041566</v>
+        <v>7041252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +2932,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669073</v>
+        <v>102632284</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,37 +2943,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461824</v>
+        <v>461886</v>
       </c>
       <c r="R25" t="n">
-        <v>7041252</v>
+        <v>7041655</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3227,12 +3008,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,22 +3028,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669065</v>
+        <v>127669047</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,10 +3075,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462058</v>
+        <v>461543</v>
       </c>
       <c r="R26" t="n">
-        <v>7041020</v>
+        <v>7041572</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3115,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,10 +3142,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127669080</v>
+        <v>127669048</v>
       </c>
       <c r="B27" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3153,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3177,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461710</v>
+        <v>461548</v>
       </c>
       <c r="R27" t="n">
-        <v>7041300</v>
+        <v>7041571</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,6 +3213,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,10 +3244,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669081</v>
+        <v>127669050</v>
       </c>
       <c r="B28" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,21 +3255,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3279,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461655</v>
+        <v>461558</v>
       </c>
       <c r="R28" t="n">
-        <v>7041293</v>
+        <v>7041569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,6 +3315,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3346,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669078</v>
+        <v>127669051</v>
       </c>
       <c r="B29" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3357,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3381,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461868</v>
+        <v>461560</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,6 +3417,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3652,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127669086</v>
+        <v>127669053</v>
       </c>
       <c r="B30" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,21 +3459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3687,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461915</v>
+        <v>461654</v>
       </c>
       <c r="R30" t="n">
-        <v>7041539</v>
+        <v>7041431</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,6 +3519,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3749,10 +3550,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127669082</v>
+        <v>127669054</v>
       </c>
       <c r="B31" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,21 +3561,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3585,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461773</v>
+        <v>461774</v>
       </c>
       <c r="R31" t="n">
-        <v>7041572</v>
+        <v>7041329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,6 +3621,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3846,10 +3652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127669090</v>
+        <v>127669055</v>
       </c>
       <c r="B32" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3857,21 +3663,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3881,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461887</v>
+        <v>461992</v>
       </c>
       <c r="R32" t="n">
-        <v>7041257</v>
+        <v>7041200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3917,6 +3723,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3943,10 +3754,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669072</v>
+        <v>127669056</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,10 +3789,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461817</v>
+        <v>461996</v>
       </c>
       <c r="R33" t="n">
-        <v>7041252</v>
+        <v>7041113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4018,7 +3829,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127669083</v>
+        <v>127669057</v>
       </c>
       <c r="B34" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4080,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461785</v>
+        <v>462115</v>
       </c>
       <c r="R34" t="n">
-        <v>7041591</v>
+        <v>7041025</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4116,6 +3927,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4142,10 +3958,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127669070</v>
+        <v>127669058</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461616</v>
+        <v>462135</v>
       </c>
       <c r="R35" t="n">
-        <v>7041389</v>
+        <v>7040973</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,10 +4060,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127669089</v>
+        <v>127669059</v>
       </c>
       <c r="B36" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,21 +4071,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4095,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461855</v>
+        <v>462135</v>
       </c>
       <c r="R36" t="n">
-        <v>7041550</v>
+        <v>7040976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,6 +4131,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4341,10 +4162,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127669097</v>
+        <v>127669060</v>
       </c>
       <c r="B37" t="n">
-        <v>88761</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,21 +4173,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461933</v>
+        <v>462105</v>
       </c>
       <c r="R37" t="n">
-        <v>7041131</v>
+        <v>7040991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,6 +4233,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4438,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127669096</v>
+        <v>127669062</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,21 +4275,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4299,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462095</v>
+        <v>462111</v>
       </c>
       <c r="R38" t="n">
-        <v>7041036</v>
+        <v>7041002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4513,7 +4339,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4540,10 +4366,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127669074</v>
+        <v>127669063</v>
       </c>
       <c r="B39" t="n">
-        <v>91767</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,16 +4377,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4401,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461699</v>
+        <v>462099</v>
       </c>
       <c r="R39" t="n">
-        <v>7041298</v>
+        <v>7041019</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,13 +4439,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4633,10 +4468,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127669059</v>
+        <v>127669064</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4668,10 +4503,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462135</v>
+        <v>462063</v>
       </c>
       <c r="R40" t="n">
-        <v>7040976</v>
+        <v>7041008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4735,10 +4570,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127669053</v>
+        <v>127669065</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4605,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461654</v>
+        <v>462058</v>
       </c>
       <c r="R41" t="n">
-        <v>7041431</v>
+        <v>7041020</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,7 +4645,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4837,10 +4672,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127669094</v>
+        <v>127669066</v>
       </c>
       <c r="B42" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,21 +4683,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4872,10 +4707,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461551</v>
+        <v>461928</v>
       </c>
       <c r="R42" t="n">
-        <v>7041522</v>
+        <v>7041135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,6 +4743,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4934,10 +4774,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127669064</v>
+        <v>127669067</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4969,10 +4809,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462063</v>
+        <v>461932</v>
       </c>
       <c r="R43" t="n">
-        <v>7041008</v>
+        <v>7041126</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,7 +4849,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,10 +4876,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127669055</v>
+        <v>127669068</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5071,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461992</v>
+        <v>461816</v>
       </c>
       <c r="R44" t="n">
-        <v>7041200</v>
+        <v>7041233</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5138,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127669066</v>
+        <v>127669069</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461928</v>
+        <v>461820</v>
       </c>
       <c r="R45" t="n">
-        <v>7041135</v>
+        <v>7041262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5240,10 +5080,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127669085</v>
+        <v>127669070</v>
       </c>
       <c r="B46" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,21 +5091,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462009</v>
+        <v>461616</v>
       </c>
       <c r="R46" t="n">
-        <v>7041536</v>
+        <v>7041389</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,6 +5151,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,10 +5182,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127669093</v>
+        <v>127669071</v>
       </c>
       <c r="B47" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5348,21 +5193,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5372,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461799</v>
+        <v>461583</v>
       </c>
       <c r="R47" t="n">
-        <v>7041221</v>
+        <v>7041458</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,6 +5253,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127669058</v>
+        <v>127669072</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5469,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462135</v>
+        <v>461817</v>
       </c>
       <c r="R48" t="n">
-        <v>7040973</v>
+        <v>7041252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,7 +5359,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5536,10 +5386,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127669087</v>
+        <v>102632603</v>
       </c>
       <c r="B49" t="n">
-        <v>91378</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5547,37 +5397,48 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461899</v>
+        <v>461841</v>
       </c>
       <c r="R49" t="n">
-        <v>7041535</v>
+        <v>7041566</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5601,12 +5462,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5621,60 +5487,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127669068</v>
+        <v>102632640</v>
       </c>
       <c r="B50" t="n">
-        <v>57673</v>
+        <v>99035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461816</v>
+        <v>461837</v>
       </c>
       <c r="R50" t="n">
-        <v>7041233</v>
+        <v>7041569</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5698,17 +5566,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,60 +5586,62 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669067</v>
+        <v>102631971</v>
       </c>
       <c r="B51" t="n">
-        <v>57673</v>
+        <v>99140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461932</v>
+        <v>461883</v>
       </c>
       <c r="R51" t="n">
-        <v>7041126</v>
+        <v>7041545</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5800,17 +5665,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5825,60 +5685,62 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669069</v>
+        <v>102632317</v>
       </c>
       <c r="B52" t="n">
-        <v>57673</v>
+        <v>99140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461820</v>
+        <v>461891</v>
       </c>
       <c r="R52" t="n">
-        <v>7041262</v>
+        <v>7041577</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5902,17 +5764,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5927,22 +5784,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127669063</v>
+        <v>102633497</v>
       </c>
       <c r="B53" t="n">
-        <v>57673</v>
+        <v>78339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5950,37 +5807,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bredbyn S, Jmt</t>
+          <t>Bredbyn 2:1, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462099</v>
+        <v>461741</v>
       </c>
       <c r="R53" t="n">
-        <v>7041019</v>
+        <v>7041627</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6004,17 +5862,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6029,22 +5882,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127669057</v>
+        <v>127669074</v>
       </c>
       <c r="B54" t="n">
-        <v>57673</v>
+        <v>92329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6052,21 +5905,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6076,10 +5929,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462115</v>
+        <v>461699</v>
       </c>
       <c r="R54" t="n">
-        <v>7041025</v>
+        <v>7041298</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6114,17 +5967,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6140,302 +5989,6 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>127669071</v>
-      </c>
-      <c r="B55" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Bredbyn S, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>461583</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7041458</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>127669075</v>
-      </c>
-      <c r="B56" t="n">
-        <v>91356</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Bredbyn S, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>461962</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7041573</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>127669046</v>
-      </c>
-      <c r="B57" t="n">
-        <v>92057</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Bredbyn S, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>462042</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7041614</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34803-2025 artfynd.xlsx
+++ b/artfynd/A 34803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102633167</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1257,6 +1287,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632948</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102633447</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102633444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1648,6 +1698,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669050</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669051</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2158,6 +2233,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669053</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2464,6 +2554,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669069</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2566,6 +2661,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669070</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669071</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2770,6 +2875,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669072</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632603</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2982,6 +3097,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632640</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3080,6 +3200,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102633497</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3178,6 +3303,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669074</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3276,6 +3406,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102631781</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3373,6 +3508,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669097</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3470,6 +3610,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669075</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3567,6 +3712,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669076</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3664,6 +3814,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669077</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3761,6 +3916,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669078</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3858,6 +4018,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669046</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3956,6 +4121,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632530</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4059,6 +4229,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102631714</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4157,6 +4332,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632314</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4255,6 +4435,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632572</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4357,6 +4542,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669095</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4459,6 +4649,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669096</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4567,6 +4762,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632284</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4669,6 +4869,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669055</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4771,6 +4976,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669056</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4873,6 +5083,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669057</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4975,6 +5190,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669058</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5077,6 +5297,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669059</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5179,6 +5404,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669060</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5281,6 +5511,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669062</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5383,6 +5618,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669063</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5485,6 +5725,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669064</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5587,6 +5832,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669065</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5689,6 +5939,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669066</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5791,6 +6046,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669067</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5890,6 +6150,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102631971</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5989,8 +6254,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>